--- a/从零开始学Slots/从零开始学Slots-00-导读与文章索引.xlsx
+++ b/从零开始学Slots/从零开始学Slots-00-导读与文章索引.xlsx
@@ -11843,6 +11843,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N56" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -14985,5 +14988,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:P190" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-00-导读与文章索引.xlsx
+++ b/从零开始学Slots/从零开始学Slots-00-导读与文章索引.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="373">
   <si>
     <r>
       <rPr>
@@ -11228,7 +11228,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -11351,6 +11351,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -11898,8 +11910,8 @@
       <c r="B4" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>32</v>
+      <c r="D4" s="31">
+        <v>46</v>
       </c>
       <c r="E4" s="14"/>
     </row>
@@ -13361,8 +13373,8 @@
       <c r="B72" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C72" s="22" t="s">
-        <v>256</v>
+      <c r="C72" s="32">
+        <v>623535430</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>257</v>
@@ -13375,8 +13387,8 @@
       <c r="B73" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C73" s="22" t="s">
-        <v>258</v>
+      <c r="C73" s="32">
+        <v>623623737</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>259</v>
@@ -13389,8 +13401,8 @@
       <c r="B74" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="C74" s="22" t="s">
-        <v>260</v>
+      <c r="C74" s="32">
+        <v>623694441</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>261</v>
@@ -13403,8 +13415,8 @@
       <c r="B75" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C75" s="22" t="s">
-        <v>262</v>
+      <c r="C75" s="32">
+        <v>623746693</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>263</v>
@@ -13417,8 +13429,8 @@
       <c r="B76" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="C76" s="22" t="s">
-        <v>264</v>
+      <c r="C76" s="32">
+        <v>623825211</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>265</v>
@@ -13431,8 +13443,8 @@
       <c r="B77" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="C77" s="22" t="s">
-        <v>266</v>
+      <c r="C77" s="32">
+        <v>624040358</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>267</v>
@@ -13445,8 +13457,8 @@
       <c r="B78" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C78" s="22" t="s">
-        <v>268</v>
+      <c r="C78" s="32">
+        <v>624144171</v>
       </c>
       <c r="D78" s="9" t="s">
         <v>269</v>
@@ -13459,8 +13471,8 @@
       <c r="B79" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="C79" s="22" t="s">
-        <v>270</v>
+      <c r="C79" s="32">
+        <v>624248081</v>
       </c>
       <c r="D79" s="9" t="s">
         <v>271</v>
@@ -13473,8 +13485,8 @@
       <c r="B80" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="C80" s="22" t="s">
-        <v>272</v>
+      <c r="C80" s="32">
+        <v>624380588</v>
       </c>
       <c r="D80" s="9" t="s">
         <v>273</v>
@@ -13487,8 +13499,8 @@
       <c r="B81" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="C81" s="22" t="s">
-        <v>274</v>
+      <c r="C81" s="32">
+        <v>624381360</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>275</v>
@@ -13501,8 +13513,8 @@
       <c r="B82" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="C82" s="22" t="s">
-        <v>276</v>
+      <c r="C82" s="32">
+        <v>624381718</v>
       </c>
       <c r="D82" s="9" t="s">
         <v>277</v>
@@ -13515,8 +13527,8 @@
       <c r="B83" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C83" s="22" t="s">
-        <v>278</v>
+      <c r="C83" s="32">
+        <v>624382144</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>279</v>
@@ -13529,8 +13541,8 @@
       <c r="B84" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="C84" s="22" t="s">
-        <v>280</v>
+      <c r="C84" s="32">
+        <v>624676796</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>281</v>
@@ -13543,8 +13555,8 @@
       <c r="B85" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="C85" s="22" t="s">
-        <v>282</v>
+      <c r="C85" s="32">
+        <v>624678060</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>283</v>
@@ -13557,8 +13569,8 @@
       <c r="B86" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="C86" s="22" t="s">
-        <v>284</v>
+      <c r="C86" s="32">
+        <v>625043502</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>285</v>
@@ -13571,8 +13583,8 @@
       <c r="B87" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="C87" s="22" t="s">
-        <v>286</v>
+      <c r="C87" s="32">
+        <v>625322021</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>287</v>
@@ -13585,8 +13597,8 @@
       <c r="B88" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="C88" s="22" t="s">
-        <v>288</v>
+      <c r="C88" s="32">
+        <v>625543717</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>289</v>
@@ -13599,8 +13611,8 @@
       <c r="B89" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="C89" s="22" t="s">
-        <v>290</v>
+      <c r="C89" s="32">
+        <v>626184549</v>
       </c>
       <c r="D89" s="26" t="s">
         <v>291</v>
@@ -13614,8 +13626,8 @@
       <c r="B90" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="C90" s="22" t="s">
-        <v>292</v>
+      <c r="C90" s="32">
+        <v>626633039</v>
       </c>
       <c r="D90" s="26" t="s">
         <v>293</v>
@@ -13629,8 +13641,8 @@
       <c r="B91" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="C91" s="22" t="s">
-        <v>294</v>
+      <c r="C91" s="32">
+        <v>626905392</v>
       </c>
       <c r="D91" s="9" t="s">
         <v>295</v>
@@ -13643,8 +13655,8 @@
       <c r="B92" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="C92" s="22" t="s">
-        <v>296</v>
+      <c r="C92" s="32">
+        <v>627152219</v>
       </c>
       <c r="D92" s="9" t="s">
         <v>297</v>
@@ -13657,8 +13669,8 @@
       <c r="B93" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C93" s="22" t="s">
-        <v>298</v>
+      <c r="C93" s="32">
+        <v>627624679</v>
       </c>
       <c r="D93" s="9" t="s">
         <v>299</v>
@@ -13671,8 +13683,8 @@
       <c r="B94" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="C94" s="22" t="s">
-        <v>300</v>
+      <c r="C94" s="32">
+        <v>628609256</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>301</v>
@@ -13685,8 +13697,8 @@
       <c r="B95" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="C95" s="22" t="s">
-        <v>302</v>
+      <c r="C95" s="32">
+        <v>628678396</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>303</v>
@@ -13699,8 +13711,8 @@
       <c r="B96" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="C96" s="22" t="s">
-        <v>304</v>
+      <c r="C96" s="32">
+        <v>629840640</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>305</v>
@@ -13713,8 +13725,8 @@
       <c r="B97" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="C97" s="22" t="s">
-        <v>306</v>
+      <c r="C97" s="32">
+        <v>630126758</v>
       </c>
       <c r="D97" s="26" t="s">
         <v>307</v>
@@ -13728,8 +13740,8 @@
       <c r="B98" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="C98" s="22" t="s">
-        <v>308</v>
+      <c r="C98" s="32">
+        <v>630384815</v>
       </c>
       <c r="D98" s="26" t="s">
         <v>309</v>
@@ -13743,8 +13755,8 @@
       <c r="B99" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="C99" s="22" t="s">
-        <v>310</v>
+      <c r="C99" s="32">
+        <v>631770497</v>
       </c>
       <c r="D99" s="26" t="s">
         <v>311</v>
@@ -13758,8 +13770,8 @@
       <c r="B100" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="C100" s="22" t="s">
-        <v>312</v>
+      <c r="C100" s="32">
+        <v>633527344</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>313</v>
@@ -13772,8 +13784,8 @@
       <c r="B101" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="C101" s="22" t="s">
-        <v>314</v>
+      <c r="C101" s="32">
+        <v>633668409</v>
       </c>
       <c r="D101" s="26" t="s">
         <v>315</v>
@@ -13787,8 +13799,8 @@
       <c r="B102" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="C102" s="22" t="s">
-        <v>316</v>
+      <c r="C102" s="32">
+        <v>634251282</v>
       </c>
       <c r="D102" s="26" t="s">
         <v>317</v>
@@ -13802,8 +13814,8 @@
       <c r="B103" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="C103" s="22" t="s">
-        <v>318</v>
+      <c r="C103" s="32">
+        <v>635308088</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>319</v>
@@ -13816,8 +13828,8 @@
       <c r="B104" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="C104" s="22" t="s">
-        <v>320</v>
+      <c r="C104" s="32">
+        <v>635407035</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>321</v>
@@ -13830,8 +13842,8 @@
       <c r="B105" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="C105" s="22" t="s">
-        <v>322</v>
+      <c r="C105" s="32">
+        <v>635423881</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>323</v>
@@ -13844,8 +13856,8 @@
       <c r="B106" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="C106" s="22" t="s">
-        <v>324</v>
+      <c r="C106" s="32">
+        <v>635633608</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>325</v>
@@ -13858,8 +13870,8 @@
       <c r="B107" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C107" s="22" t="s">
-        <v>326</v>
+      <c r="C107" s="32">
+        <v>635847235</v>
       </c>
       <c r="D107" s="26" t="s">
         <v>327</v>
@@ -13873,8 +13885,8 @@
       <c r="B108" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C108" s="22" t="s">
-        <v>328</v>
+      <c r="C108" s="32">
+        <v>636564067</v>
       </c>
       <c r="D108" s="26" t="s">
         <v>329</v>
@@ -13888,8 +13900,8 @@
       <c r="B109" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C109" s="22" t="s">
-        <v>330</v>
+      <c r="C109" s="32">
+        <v>636933475</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>331</v>
@@ -13902,8 +13914,8 @@
       <c r="B110" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="C110" s="22" t="s">
-        <v>332</v>
+      <c r="C110" s="32">
+        <v>637203163</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>333</v>
@@ -13916,8 +13928,8 @@
       <c r="B111" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C111" s="22" t="s">
-        <v>334</v>
+      <c r="C111" s="32">
+        <v>637469752</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>335</v>
@@ -13930,8 +13942,8 @@
       <c r="B112" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="C112" s="22" t="s">
-        <v>336</v>
+      <c r="C112" s="32">
+        <v>638130127</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>337</v>
@@ -13944,8 +13956,8 @@
       <c r="B113" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C113" s="22" t="s">
-        <v>338</v>
+      <c r="C113" s="32">
+        <v>638757841</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>339</v>
@@ -13958,8 +13970,8 @@
       <c r="B114" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="C114" s="22" t="s">
-        <v>340</v>
+      <c r="C114" s="32">
+        <v>639548656</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>341</v>
@@ -13972,8 +13984,8 @@
       <c r="B115" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C115" s="22" t="s">
-        <v>342</v>
+      <c r="C115" s="32">
+        <v>642911545</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>343</v>
@@ -13986,8 +13998,8 @@
       <c r="B116" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="C116" s="22" t="s">
-        <v>344</v>
+      <c r="C116" s="32">
+        <v>649393400</v>
       </c>
       <c r="D116" s="9" t="s">
         <v>345</v>
@@ -14872,8 +14884,8 @@
       <c r="H167" s="7"/>
     </row>
     <row r="168" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="4" t="s">
-        <v>370</v>
+      <c r="A168" s="33">
+        <v>45</v>
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>

--- a/从零开始学Slots/从零开始学Slots-00-导读与文章索引.xlsx
+++ b/从零开始学Slots/从零开始学Slots-00-导读与文章索引.xlsx
@@ -11055,10 +11055,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -11228,7 +11229,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -11363,6 +11364,10 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -11973,7 +11978,7 @@
       <c r="A10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="34" t="n">
         <f aca="false">IF($B$4=0,0,$B$6/$B$4)</f>
         <v>1</v>
       </c>
@@ -12012,7 +12017,7 @@
       <c r="A13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="34" t="n">
         <f aca="false">IF($B$5=0,0,$B$12/($B$5-1))</f>
         <v>1</v>
       </c>
